--- a/excel/Revolut Robo.xlsx
+++ b/excel/Revolut Robo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Revolut\Robo Advisor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-dashboard-clean\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7537B3-69B7-48F6-8E3B-407C99C0C244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F584561D-901F-43F5-BB93-DF78FF5D7637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apžvalga" sheetId="77" r:id="rId1"/>
@@ -815,7 +815,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1067,6 +1067,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4596,14 +4597,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM34"/>
+  <dimension ref="A1:AS34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="39" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
         <v>90</v>
       </c>
@@ -4654,7 +4655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="70"/>
       <c r="B2" s="3" t="s">
         <v>71</v>
@@ -4766,8 +4767,11 @@
       </c>
       <c r="AL2" s="69"/>
       <c r="AM2" s="69"/>
-    </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AS2" s="95">
+        <v>5.33E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="str">
         <f>'2024.02'!A1</f>
         <v>2024.02</v>
@@ -4904,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="62" t="str">
         <f>'2024.03'!A1</f>
         <v>2024.03</v>
@@ -5041,7 +5045,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="62" t="str">
         <f>'2024.04'!A1</f>
         <v>2024.04</v>
@@ -5178,7 +5182,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="str">
         <f>'2024.05'!A1</f>
         <v>2024.05</v>
@@ -5315,7 +5319,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="62" t="str">
         <f>'2024.06'!A1</f>
         <v>2024.06</v>
@@ -5452,7 +5456,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="62" t="str">
         <f>'2024.07'!A1</f>
         <v>2024.07</v>
@@ -5589,7 +5593,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="62" t="str">
         <f>'2024.08'!A1</f>
         <v>2024.08</v>
@@ -5726,7 +5730,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="62" t="str">
         <f>'2024.09'!A1</f>
         <v>2024.09</v>
@@ -5863,7 +5867,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="62" t="str">
         <f>'2024.10'!A1</f>
         <v>2024.10</v>
@@ -6000,7 +6004,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="62" t="str">
         <f>'2024.11'!A1</f>
         <v>2024.11</v>
@@ -6137,7 +6141,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="str">
         <f>'2024.12'!A1</f>
         <v>2024.12</v>
@@ -6274,7 +6278,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="str">
         <f>'2025.01'!A1</f>
         <v>2025.01</v>
@@ -6411,7 +6415,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="62" t="str">
         <f>'2025.02'!A1</f>
         <v>2025.02</v>
@@ -6548,7 +6552,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="62" t="str">
         <f>'2025.03'!A1</f>
         <v>2025.03</v>
